--- a/bin/Debug/net8.0/Files/rajdhani-day-penal-chart.xlsx
+++ b/bin/Debug/net8.0/Files/rajdhani-day-penal-chart.xlsx
@@ -34019,13 +34019,13 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="E459" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F459" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G459" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H459" s="3" t="s">
         <x:v>41</x:v>
